--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0093.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0093.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Mỗi lần Gugloo ăn đồ từ tay ta, nó lại nhổ ra ngay lập tức... Nhưng đồ của Zahira thì không hề hấn gì, sạch sẽ gọn gàng.</t>
+          <t>Mỗi lần Gugloo ăn đồ từ tay tao, nó lại nhổ ra ngay lập tức... Nhưng đồ của Zahira thì không hề hấn gì, sạch sẽ gọn gàng.</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Chúng còn không tính nhẩm được phép nhân năm chữ số. Tin được à? Ta thà tin ta là Exostrider còn hơn.</t>
+          <t>Chúng còn không tính nhẩm được phép nhân năm chữ số. Tin được à? Tao thà tin tao là Exostrider còn hơn.</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Vậy à? Thế thì nói ta nghe tại sao nó lại cuộn tròn trên bụng ta mỗi đêm hả? Rõ ràng nó thích ta nhất mà.</t>
+          <t>Vậy à? Thế thì nói tao nghe tại sao nó lại cuộn tròn trên bụng tao mỗi đêm hả? Rõ ràng nó thích tao nhất mà.</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Ta đang làm một dự án cần thu thập dữ liệu từ Atuja... Ta đã muốn gặp ngươi từ hôm qua rồi!</t>
+          <t>Tao đang làm một dự án cần thu thập dữ liệu từ Atuja... Tao đã muốn gặp mày từ hôm qua rồi!</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Cậu chắc thứ này chặn được Bão Hư Không à?</t>
+          <t>Mày chắc thứ này chặn được Bão Hư Không à?</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Nói ta nghe này: Liệu máy bay không người lái có cần thời gian để xả két không hả?</t>
+          <t>Nói tao nghe này: Liệu máy bay không người lái có cần thời gian để xả két không hả?</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Nhìn thẳng vào mắt ta và trả lời câu hỏi该死 này đi!</t>
+          <t>Nhìn thẳng vào mắt tao và trả lời câu hỏi该死 này đi!</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Nói ta nghe này: Liệu máy bay không người lái có cần thời gian để xả két không hả?</t>
+          <t>Nói tao nghe này: Liệu máy bay không người lái có cần thời gian để xả két không hả?</t>
         </is>
       </c>
     </row>
